--- a/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,76; 11,24</t>
+          <t>5,39; 10,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,71</t>
+          <t>4,27; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,07</t>
+          <t>5,6; 9,12</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,15</t>
+          <t>5,19; 10,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,52</t>
+          <t>4,29; 8,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,69</t>
+          <t>5,27; 8,32</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 9,57</t>
+          <t>1,92; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,75</t>
+          <t>6,56; 13,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 9,72</t>
+          <t>2,75; 9,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,76</t>
+          <t>6,8; 10,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 64,72</t>
+          <t>8,91; 63,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 44,51</t>
+          <t>8,78; 41,99</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,87; 21,71</t>
+          <t>14,0; 21,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 15,26</t>
+          <t>9,39; 15,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,83</t>
+          <t>11,65; 16,67</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 13,17</t>
+          <t>2,01; 12,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,52</t>
+          <t>8,43; 12,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,31</t>
+          <t>7,5; 11,47</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 10,07</t>
+          <t>6,87; 9,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 31,04</t>
+          <t>9,38; 31,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 20,17</t>
+          <t>8,93; 21,01</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29096; 56788</t>
+          <t>27210; 54086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20197; 38846</t>
+          <t>19055; 37623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54261; 86266</t>
+          <t>53267; 86716</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23300; 45902</t>
+          <t>23467; 46088</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16884; 32604</t>
+          <t>16400; 32301</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43568; 72551</t>
+          <t>44004; 69455</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12552; 63858</t>
+          <t>12834; 65361</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10626; 22957</t>
+          <t>10943; 22890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18964; 81115</t>
+          <t>22947; 82866</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368855</t>
+          <t>368856</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72808; 111303</t>
+          <t>70349; 111790</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90004; 632412</t>
+          <t>87034; 621770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174797; 895588</t>
+          <t>176745; 844804</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65881; 103129</t>
+          <t>66490; 103119</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77113; 128400</t>
+          <t>78969; 132808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154633; 221531</t>
+          <t>153337; 219397</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5568; 31682</t>
+          <t>4827; 30903</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65232; 95227</t>
+          <t>64103; 93738</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75448; 113254</t>
+          <t>75055; 114842</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>229283; 339891</t>
+          <t>231870; 336985</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>339142; 1109532</t>
+          <t>335407; 1113029</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621512; 1402046</t>
+          <t>620814; 1460386</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,71</t>
+          <t>5,89; 11,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,43</t>
+          <t>4,91; 9,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,12</t>
+          <t>6,0; 9,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,19</t>
+          <t>5,18; 9,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,44</t>
+          <t>4,59; 8,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,32</t>
+          <t>5,47; 8,78</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,8</t>
+          <t>6,37; 11,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,71</t>
+          <t>6,57; 13,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 9,93</t>
+          <t>7,15; 11,59</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,8</t>
+          <t>7,18; 10,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 63,63</t>
+          <t>8,29; 12,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,78; 41,99</t>
+          <t>8,2; 10,77</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,0; 21,71</t>
+          <t>14,98; 21,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 15,79</t>
+          <t>12,44; 16,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,67</t>
+          <t>14,17; 17,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,85</t>
+          <t>2,82; 14,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,43; 12,32</t>
+          <t>8,75; 12,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,5; 11,47</t>
+          <t>8,27; 12,22</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,98</t>
+          <t>8,87; 11,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,38; 31,13</t>
+          <t>9,44; 11,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 21,01</t>
+          <t>9,47; 10,85</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39726</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27731</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>78054</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27210; 54086</t>
+          <t>32414; 61579</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19055; 37623</t>
+          <t>23888; 45470</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53267; 86716</t>
+          <t>62236; 99289</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32558</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>27579</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55597</t>
+          <t>62850</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23467; 46088</t>
+          <t>25039; 47780</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16400; 32301</t>
+          <t>19419; 37760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44004; 69455</t>
+          <t>49589; 79544</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53988</t>
+          <t>59970</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12834; 65361</t>
+          <t>29998; 53763</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10943; 22890</t>
+          <t>12326; 25849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22947; 82866</t>
+          <t>47063; 76252</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>89385</t>
+          <t>101203</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>279471</t>
+          <t>85597</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>368856</t>
+          <t>186800</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70349; 111790</t>
+          <t>81261; 121838</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87034; 621770</t>
+          <t>71216; 103871</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176745; 844804</t>
+          <t>163323; 214562</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82619</t>
+          <t>102765</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>106979</t>
+          <t>119456</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189598</t>
+          <t>222220</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66490; 103119</t>
+          <t>85100; 123901</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78969; 132808</t>
+          <t>103345; 139283</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153337; 219397</t>
+          <t>198178; 249876</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>78711</t>
+          <t>91770</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92284</t>
+          <t>107383</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4827; 30903</t>
+          <t>6686; 33310</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64103; 93738</t>
+          <t>73839; 109000</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75055; 114842</t>
+          <t>89370; 132044</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>295830</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>531950</t>
+          <t>375533</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>827779</t>
+          <t>717278</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>231870; 336985</t>
+          <t>305181; 389235</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>335407; 1113029</t>
+          <t>342756; 409053</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620814; 1460386</t>
+          <t>669566; 767177</t>
         </is>
       </c>
     </row>
